--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DDE3D3-9DFB-46A7-A48E-DB707E572B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95502699-11CC-41F8-B077-9C781BEF21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="3" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="114">
   <si>
     <t>Project_Name</t>
   </si>
@@ -335,9 +335,6 @@
     <t>testAddNewTask_FromTaskPage</t>
   </si>
   <si>
-    <t>Meeting</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -356,12 +353,6 @@
     <t>testAddNewTask_FromProjectPage</t>
   </si>
   <si>
-    <t>Discuss</t>
-  </si>
-  <si>
-    <t>03/05/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">nhanhotiennghi </t>
   </si>
   <si>
@@ -375,6 +366,24 @@
   </si>
   <si>
     <t>11</t>
+  </si>
+  <si>
+    <t>Task_Number</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>Status_Task</t>
+  </si>
+  <si>
+    <t>Discuss 2</t>
+  </si>
+  <si>
+    <t>Meeting 2</t>
   </si>
 </sst>
 </file>
@@ -988,7 +997,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
         <v>57</v>
@@ -1233,146 +1242,152 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20CCAF4C-440A-4CC0-BE66-266F410C1500}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="20.77734375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="10" t="str">
+      <c r="K2" s="10" t="str">
         <f xml:space="preserve"> Project!B2</f>
         <v>2393</v>
       </c>
-      <c r="J2" s="10" t="str">
+      <c r="L2" s="10" t="str">
         <f xml:space="preserve"> Project!C2</f>
         <v>Tổ ấm nhỏ</v>
       </c>
-      <c r="K2" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="M2" s="10" t="s">
         <v>106</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="G3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="I3" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="10" t="str">
+      <c r="K3" s="10" t="str">
         <f xml:space="preserve"> Project!B4</f>
         <v>2389</v>
       </c>
-      <c r="J3" s="10" t="str">
+      <c r="L3" s="10" t="str">
         <f xml:space="preserve"> Project!C4</f>
         <v>Xây nhà cho bé</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="M3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="10" t="s">
-        <v>108</v>
+      <c r="P3" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95502699-11CC-41F8-B077-9C781BEF21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3ABCD1-D894-423B-B3F5-53A4DD413F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="3" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="116">
   <si>
     <t>Project_Name</t>
   </si>
@@ -212,9 +212,6 @@
     <t>01-06-2026</t>
   </si>
   <si>
-    <t>Công ty TNHH VT</t>
-  </si>
-  <si>
     <t>093yyzzxxx</t>
   </si>
   <si>
@@ -236,9 +233,6 @@
     <t>Japan</t>
   </si>
   <si>
-    <t>Công ty VT YHL</t>
-  </si>
-  <si>
     <t>Cancelled</t>
   </si>
   <si>
@@ -269,121 +263,133 @@
     <t>ADD - EDIT</t>
   </si>
   <si>
+    <t xml:space="preserve">nhacuabe </t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 2026</t>
+  </si>
+  <si>
+    <t>Tổ ấm nhỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thạch cao </t>
+  </si>
+  <si>
+    <t xml:space="preserve">online </t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Hourly_Rate</t>
+  </si>
+  <si>
+    <t>Due_Date</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Repeat _Every</t>
+  </si>
+  <si>
+    <t>Related_To</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Assignees</t>
+  </si>
+  <si>
+    <t>Followers</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 05/2026</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>testAddNewTask_FromTaskPage</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>testAddNewTask_FromProjectPage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nhanhotiennghi </t>
+  </si>
+  <si>
+    <t>Bàn về nguyên vật liệu</t>
+  </si>
+  <si>
+    <t>Lên plan</t>
+  </si>
+  <si>
+    <t>AssigneesProject ManagerAdmin Anh TesterAdmin Example</t>
+  </si>
+  <si>
+    <t>Task_Number</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>Status_Task</t>
+  </si>
+  <si>
+    <t>Discuss về plan</t>
+  </si>
+  <si>
+    <t>Meeting lên plan</t>
+  </si>
+  <si>
+    <t>submitDataForNewCustomer</t>
+  </si>
+  <si>
+    <t>submitData_WithNullCompany</t>
+  </si>
+  <si>
     <t>Passed</t>
   </si>
   <si>
-    <t xml:space="preserve">nhacuabe </t>
-  </si>
-  <si>
-    <t>Mua hàng qua app 2026</t>
-  </si>
-  <si>
-    <t>2389</t>
-  </si>
-  <si>
-    <t>Tổ ấm nhỏ</t>
-  </si>
-  <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9093</t>
-  </si>
-  <si>
-    <t>2393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thạch cao </t>
-  </si>
-  <si>
-    <t xml:space="preserve">online </t>
-  </si>
-  <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>Hourly_Rate</t>
-  </si>
-  <si>
-    <t>Due_Date</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Repeat _Every</t>
-  </si>
-  <si>
-    <t>Related_To</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Assignees</t>
-  </si>
-  <si>
-    <t>Followers</t>
-  </si>
-  <si>
-    <t>Mua hàng qua app 05/2026</t>
-  </si>
-  <si>
-    <t>2398</t>
-  </si>
-  <si>
-    <t>Task Description</t>
-  </si>
-  <si>
-    <t>testAddNewTask_FromTaskPage</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>01/06/2026</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>testAddNewTask_FromProjectPage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nhanhotiennghi </t>
-  </si>
-  <si>
-    <t>Bàn về nguyên vật liệu</t>
-  </si>
-  <si>
-    <t>Lên plan</t>
-  </si>
-  <si>
-    <t>AssigneesProject ManagerAdmin Anh TesterAdmin Example</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Task_Number</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>Status_Task</t>
-  </si>
-  <si>
-    <t>Discuss 2</t>
-  </si>
-  <si>
-    <t>Meeting 2</t>
+    <t>https://crm.anhtester.com/admin/clients/client/9148</t>
+  </si>
+  <si>
+    <t>2451</t>
+  </si>
+  <si>
+    <t>Công ty GM</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9150</t>
+  </si>
+  <si>
+    <t>2456</t>
+  </si>
+  <si>
+    <t>2457</t>
+  </si>
+  <si>
+    <t>Customer_Number</t>
   </si>
 </sst>
 </file>
@@ -443,39 +449,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -814,50 +848,50 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="21.77734375" style="4"/>
+    <col min="1" max="16384" width="21.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -869,162 +903,191 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="15" width="21.5546875" style="15"/>
+    <col min="16" max="16" width="21.5546875" style="13"/>
+    <col min="17" max="16384" width="21.5546875" style="15"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="K3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="17">
+        <v>10</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I4" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="I3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="N4" s="15" t="s">
         <v>62</v>
-      </c>
-      <c r="L3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1036,200 +1099,224 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="16.5546875" style="6"/>
-    <col min="4" max="4" width="18.5546875" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="16.5546875" style="6"/>
+    <col min="1" max="1" width="16.5546875" style="3"/>
+    <col min="2" max="2" width="16.5546875" style="13"/>
+    <col min="3" max="4" width="16.5546875" style="3"/>
+    <col min="5" max="5" width="18.5546875" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="16.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <f xml:space="preserve"> Customer!A3</f>
-        <v>Công ty TNHH VT</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="11" t="str">
+        <f>Customer!P2</f>
+        <v>https://crm.anhtester.com/admin/clients/client/9148</v>
+      </c>
+      <c r="E2" s="3" t="str">
+        <f>Customer!C2</f>
+        <v>Công ty CP YHL</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="11" t="str">
+        <f>Customer!P3</f>
+        <v>https://crm.anhtester.com/admin/clients/client/9150</v>
+      </c>
+      <c r="E3" s="15" t="str">
+        <f>Customer!C3</f>
+        <v>Công ty GM</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="19" t="str">
+        <f>B3</f>
+        <v>2456</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="11" t="str">
+        <f>Customer!P2</f>
+        <v>https://crm.anhtester.com/admin/clients/client/9148</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <f>Customer!C2</f>
+        <v>Công ty CP YHL</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f>Customer!P3</f>
+        <v>https://crm.anhtester.com/admin/clients/client/9150</v>
+      </c>
+      <c r="E5" s="15" t="str">
+        <f>Customer!C3</f>
+        <v>Công ty GM</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="7">
-        <v>3</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <f>B3</f>
-        <v>2389</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1245,149 +1332,149 @@
   <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="10"/>
+    <col min="1" max="16384" width="20.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="10" t="s">
+      <c r="O1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="N1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="K2" s="10" t="str">
+      <c r="I2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="5" t="str">
         <f xml:space="preserve"> Project!B2</f>
-        <v>2393</v>
-      </c>
-      <c r="L2" s="10" t="str">
+        <v>2451</v>
+      </c>
+      <c r="L2" s="5" t="str">
         <f xml:space="preserve"> Project!C2</f>
         <v>Tổ ấm nhỏ</v>
       </c>
-      <c r="M2" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>104</v>
+      <c r="M2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="A3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="10" t="str">
+      <c r="F3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <f xml:space="preserve"> Project!B4</f>
-        <v>2389</v>
-      </c>
-      <c r="L3" s="10" t="str">
+        <v>2452</v>
+      </c>
+      <c r="L3" s="5" t="str">
         <f xml:space="preserve"> Project!C4</f>
         <v>Xây nhà cho bé</v>
       </c>
-      <c r="M3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>105</v>
+      <c r="M3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3ABCD1-D894-423B-B3F5-53A4DD413F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B91974B-15F0-4EED-AA1A-74455A71A437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
   <si>
     <t>Project_Name</t>
   </si>
@@ -221,9 +221,6 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>Công ty CP YHL</t>
-  </si>
-  <si>
     <t>Wakayama</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>30-06-2028</t>
   </si>
   <si>
-    <t>Xây nhà cho bé</t>
-  </si>
-  <si>
     <t>Not Started</t>
   </si>
   <si>
@@ -269,9 +263,6 @@
     <t>Mua hàng qua app 2026</t>
   </si>
   <si>
-    <t>Tổ ấm nhỏ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thạch cao </t>
   </si>
   <si>
@@ -344,58 +335,71 @@
     <t>AssigneesProject ManagerAdmin Anh TesterAdmin Example</t>
   </si>
   <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>submitDataForNewCustomer</t>
+  </si>
+  <si>
+    <t>submitData_WithNullCompany</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9148</t>
+  </si>
+  <si>
+    <t>2451</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9150</t>
+  </si>
+  <si>
+    <t>2456</t>
+  </si>
+  <si>
+    <t>2457</t>
+  </si>
+  <si>
+    <t>Customer_Number</t>
+  </si>
+  <si>
     <t>Task_Number</t>
   </si>
   <si>
-    <t>10/05/2026</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>Status_Task</t>
-  </si>
-  <si>
-    <t>Discuss về plan</t>
-  </si>
-  <si>
-    <t>Meeting lên plan</t>
-  </si>
-  <si>
-    <t>submitDataForNewCustomer</t>
-  </si>
-  <si>
-    <t>submitData_WithNullCompany</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9148</t>
-  </si>
-  <si>
-    <t>2451</t>
-  </si>
-  <si>
-    <t>Công ty GM</t>
-  </si>
-  <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9150</t>
-  </si>
-  <si>
-    <t>2456</t>
-  </si>
-  <si>
-    <t>2457</t>
-  </si>
-  <si>
-    <t>Customer_Number</t>
+    <t>Chuẩn bị vật liệu</t>
+  </si>
+  <si>
+    <t>Công ty vật liệu YHL</t>
+  </si>
+  <si>
+    <t>Công ty thiết kế GM</t>
+  </si>
+  <si>
+    <t>Nhà là nơi để về</t>
+  </si>
+  <si>
+    <t>Nhà tình thương</t>
+  </si>
+  <si>
+    <t>2458</t>
+  </si>
+  <si>
+    <t>2459</t>
+  </si>
+  <si>
+    <t>1834</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -411,7 +415,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,6 +440,12 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -449,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -469,18 +479,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -490,26 +488,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -848,17 +864,17 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="21.77734375" style="1"/>
+    <col min="1" max="16384" style="1" width="21.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -906,55 +922,55 @@
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="15" width="21.5546875" style="15"/>
-    <col min="16" max="16" width="21.5546875" style="13"/>
-    <col min="17" max="16384" width="21.5546875" style="15"/>
+    <col min="1" max="15" style="5" width="21.5546875"/>
+    <col min="16" max="16" style="9" width="21.5546875"/>
+    <col min="17" max="16384" style="5" width="21.5546875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="8" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="8" t="s">
@@ -962,132 +978,132 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="A2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>109</v>
+      <c r="O2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="A3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="N3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="M3" s="17" t="s">
+      <c r="N4" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="17">
-        <v>10</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1102,18 +1118,18 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" style="3"/>
-    <col min="2" max="2" width="16.5546875" style="13"/>
-    <col min="3" max="4" width="16.5546875" style="3"/>
-    <col min="5" max="5" width="18.5546875" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="16.5546875" style="3"/>
+    <col min="1" max="1" style="3" width="16.5546875"/>
+    <col min="2" max="2" style="9" width="16.5546875"/>
+    <col min="3" max="4" style="3" width="16.5546875"/>
+    <col min="5" max="5" customWidth="true" style="3" width="18.5546875"/>
+    <col min="6" max="16384" style="3" width="16.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -1154,19 +1170,19 @@
       <c r="A2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>110</v>
+      <c r="B2" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="11" t="str">
+        <v>112</v>
+      </c>
+      <c r="D2" s="7" t="str">
         <f>Customer!P2</f>
         <v>https://crm.anhtester.com/admin/clients/client/9148</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>Customer!C2</f>
-        <v>Công ty CP YHL</v>
+        <v>Công ty vật liệu YHL</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>35</v>
@@ -1187,7 +1203,7 @@
         <v>41</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>44</v>
@@ -1195,27 +1211,27 @@
     </row>
     <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="11" t="str">
+      <c r="D3" s="7" t="str">
         <f>Customer!P3</f>
         <v>https://crm.anhtester.com/admin/clients/client/9150</v>
       </c>
-      <c r="E3" s="15" t="str">
+      <c r="E3" s="10" t="str">
         <f>Customer!C3</f>
-        <v>Công ty GM</v>
+        <v>Công ty thiết kế GM</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H3" s="4">
         <v>3</v>
@@ -1227,7 +1243,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>50</v>
@@ -1237,29 +1253,29 @@
       <c r="A4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="14" t="str">
         <f>B3</f>
         <v>2456</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="11" t="str">
+        <v>113</v>
+      </c>
+      <c r="D4" s="7" t="str">
         <f>Customer!P2</f>
         <v>https://crm.anhtester.com/admin/clients/client/9148</v>
       </c>
       <c r="E4" s="3" t="str">
         <f>Customer!C2</f>
-        <v>Công ty CP YHL</v>
+        <v>Công ty vật liệu YHL</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>37</v>
@@ -1268,53 +1284,53 @@
         <v>55</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>114</v>
+      <c r="B5" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="11" t="str">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7" t="str">
         <f>Customer!P3</f>
         <v>https://crm.anhtester.com/admin/clients/client/9150</v>
       </c>
-      <c r="E5" s="15" t="str">
+      <c r="E5" s="10" t="str">
         <f>Customer!C3</f>
-        <v>Công ty GM</v>
+        <v>Công ty thiết kế GM</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>50</v>
@@ -1329,152 +1345,153 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20CCAF4C-440A-4CC0-BE66-266F410C1500}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="5"/>
+    <col min="1" max="16384" style="5" width="20.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="N1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <f xml:space="preserve"> Project!B2</f>
+        <v>2459</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <f xml:space="preserve"> Project!C2</f>
+        <v>Nhà là nơi để về</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="9" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="F3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <f xml:space="preserve"> Project!B4</f>
+        <v>2456</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <f xml:space="preserve"> Project!C4</f>
+        <v>Nhà tình thương</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <f xml:space="preserve"> Project!B2</f>
-        <v>2451</v>
-      </c>
-      <c r="L2" s="5" t="str">
-        <f xml:space="preserve"> Project!C2</f>
-        <v>Tổ ấm nhỏ</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <f xml:space="preserve"> Project!B4</f>
-        <v>2452</v>
-      </c>
-      <c r="L3" s="5" t="str">
-        <f xml:space="preserve"> Project!C4</f>
-        <v>Xây nhà cho bé</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B91974B-15F0-4EED-AA1A-74455A71A437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8CA9E5-C86D-4AB5-94C5-92186AEE75CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="111">
   <si>
     <t>Project_Name</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Giá cả hợp lý, chất liệu hợp thời</t>
   </si>
   <si>
-    <t>URL_Customer</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -350,24 +347,12 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9148</t>
-  </si>
-  <si>
-    <t>2451</t>
-  </si>
-  <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9150</t>
-  </si>
-  <si>
     <t>2456</t>
   </si>
   <si>
     <t>2457</t>
   </si>
   <si>
-    <t>Customer_Number</t>
-  </si>
-  <si>
     <t>Task_Number</t>
   </si>
   <si>
@@ -384,9 +369,6 @@
   </si>
   <si>
     <t>Nhà tình thương</t>
-  </si>
-  <si>
-    <t>2458</t>
   </si>
   <si>
     <t>2459</t>
@@ -399,7 +381,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -415,7 +396,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,12 +421,6 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill/>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -459,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -479,9 +454,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -491,40 +463,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -864,17 +815,17 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" style="1" width="21.77734375"/>
+    <col min="1" max="16384" width="21.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -919,191 +870,177 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="15" style="5" width="21.5546875"/>
-    <col min="16" max="16" style="9" width="21.5546875"/>
-    <col min="17" max="16384" style="5" width="21.5546875"/>
+    <col min="1" max="16384" width="21.5546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="8" t="s">
+    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N2" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N3" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="6">
+        <v>99</v>
+      </c>
+      <c r="C4" s="6">
         <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1115,225 +1052,206 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="3" width="16.5546875"/>
-    <col min="2" max="2" style="9" width="16.5546875"/>
-    <col min="3" max="4" style="3" width="16.5546875"/>
-    <col min="5" max="5" customWidth="true" style="3" width="18.5546875"/>
-    <col min="6" max="16384" style="3" width="16.5546875"/>
+    <col min="1" max="1" width="16.5546875" style="3"/>
+    <col min="2" max="2" width="16.5546875" style="8"/>
+    <col min="3" max="3" width="16.5546875" style="3"/>
+    <col min="4" max="4" width="18.5546875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="16.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B2" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>Customer!B2</f>
+        <v>Công ty vật liệu YHL</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>Customer!B3</f>
+        <v>Công ty thiết kế GM</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="7" t="str">
-        <f>Customer!P2</f>
-        <v>https://crm.anhtester.com/admin/clients/client/9148</v>
-      </c>
-      <c r="E2" s="3" t="str">
-        <f>Customer!C2</f>
-        <v>Công ty vật liệu YHL</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <f>Customer!P3</f>
-        <v>https://crm.anhtester.com/admin/clients/client/9150</v>
-      </c>
-      <c r="E3" s="10" t="str">
-        <f>Customer!C3</f>
-        <v>Công ty thiết kế GM</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="4">
-        <v>3</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="14" t="str">
+      <c r="B4" s="12" t="str">
         <f>B3</f>
         <v>2456</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f>Customer!P2</f>
-        <v>https://crm.anhtester.com/admin/clients/client/9148</v>
-      </c>
-      <c r="E4" s="3" t="str">
-        <f>Customer!C2</f>
+        <v>108</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f>Customer!B2</f>
         <v>Công ty vật liệu YHL</v>
       </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="F4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <f>Customer!B3</f>
+        <v>Công ty thiết kế GM</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="F5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <f>Customer!P3</f>
-        <v>https://crm.anhtester.com/admin/clients/client/9150</v>
-      </c>
-      <c r="E5" s="10" t="str">
-        <f>Customer!C3</f>
-        <v>Công ty thiết kế GM</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>67</v>
+      <c r="K5" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1348,83 +1266,83 @@
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" style="5" width="20.77734375"/>
+    <col min="1" max="16384" width="20.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="8" t="s">
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>85</v>
+      <c r="O1" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>116</v>
+        <v>91</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="G2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="I2" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J2" s="5" t="str">
         <f xml:space="preserve"> Project!B2</f>
@@ -1435,43 +1353,43 @@
         <v>Nhà là nơi để về</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J3" s="5" t="str">
         <f xml:space="preserve"> Project!B4</f>
@@ -1482,16 +1400,16 @@
         <v>Nhà tình thương</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="122">
   <si>
     <t>Project_Name</t>
   </si>
@@ -375,12 +375,46 @@
   </si>
   <si>
     <t>1834</t>
+  </si>
+  <si>
+    <t>2460</t>
+  </si>
+  <si>
+    <t>2461</t>
+  </si>
+  <si>
+    <t>2462</t>
+  </si>
+  <si>
+    <t>1835</t>
+  </si>
+  <si>
+    <t>1836</t>
+  </si>
+  <si>
+    <t>2463</t>
+  </si>
+  <si>
+    <t>2464</t>
+  </si>
+  <si>
+    <t>2465</t>
+  </si>
+  <si>
+    <t>2466</t>
+  </si>
+  <si>
+    <t>1837</t>
+  </si>
+  <si>
+    <t>1838</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -396,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +455,9 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -434,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -476,6 +513,54 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,7 +900,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="21.77734375" style="1"/>
+    <col min="1" max="16384" style="1" width="21.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -873,7 +958,7 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="21.5546875" style="5"/>
+    <col min="1" max="16384" style="5" width="21.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -960,7 +1045,7 @@
       <c r="M2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="23" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1055,11 +1140,11 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" style="3"/>
-    <col min="2" max="2" width="16.5546875" style="8"/>
-    <col min="3" max="3" width="16.5546875" style="3"/>
-    <col min="4" max="4" width="18.5546875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="16.5546875" style="3"/>
+    <col min="1" max="1" style="3" width="16.5546875"/>
+    <col min="2" max="2" style="8" width="16.5546875"/>
+    <col min="3" max="3" style="3" width="16.5546875"/>
+    <col min="4" max="4" customWidth="true" style="3" width="18.5546875"/>
+    <col min="5" max="16384" style="3" width="16.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1104,8 +1189,8 @@
       <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>109</v>
+      <c r="B2" s="28" t="s">
+        <v>117</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>107</v>
@@ -1143,8 +1228,8 @@
       <c r="A3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>101</v>
+      <c r="B3" s="25" t="s">
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>71</v>
@@ -1179,9 +1264,9 @@
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="12" t="str">
+      <c r="B4" s="26" t="str">
         <f>B3</f>
-        <v>2456</v>
+        <v>2465</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>108</v>
@@ -1219,8 +1304,8 @@
       <c r="A5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>102</v>
+      <c r="B5" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>83</v>
@@ -1266,7 +1351,7 @@
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="5"/>
+    <col min="1" max="16384" style="5" width="20.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1320,8 +1405,8 @@
       <c r="A2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>110</v>
+      <c r="B2" s="29" t="s">
+        <v>120</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>94</v>
@@ -1346,7 +1431,7 @@
       </c>
       <c r="J2" s="5" t="str">
         <f xml:space="preserve"> Project!B2</f>
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="K2" s="5" t="str">
         <f xml:space="preserve"> Project!C2</f>
@@ -1369,7 +1454,9 @@
       <c r="A3" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="13"/>
+      <c r="B3" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>104</v>
       </c>
@@ -1393,7 +1480,7 @@
       </c>
       <c r="J3" s="5" t="str">
         <f xml:space="preserve"> Project!B4</f>
-        <v>2456</v>
+        <v>2465</v>
       </c>
       <c r="K3" s="5" t="str">
         <f xml:space="preserve"> Project!C4</f>
